--- a/docs/小程序配置表.xlsx
+++ b/docs/小程序配置表.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="28800" windowHeight="13660"/>
+    <workbookView windowWidth="30240" windowHeight="14640"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="35" uniqueCount="29">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="40" uniqueCount="34">
   <si>
     <t>场景名</t>
   </si>
@@ -114,6 +114,21 @@
   </si>
   <si>
     <t>开始时间（每天早上 6 点）、活动名称（期次名称+“晨读营”）、活动内容（当天学习课程名称）、参与方式（进入凡人共读小程序）</t>
+  </si>
+  <si>
+    <t>小凡看见发布</t>
+  </si>
+  <si>
+    <t>7Q501HNbbT7_GqaBsoj71eKIhVYUFwRU097Q3r8d5_M</t>
+  </si>
+  <si>
+    <t>作者（固定就是“小凡看见”）、项目名称（期次名称）、发布标题（当天学习课程名称）、发布时间（小凡看见发布时间）</t>
+  </si>
+  <si>
+    <t>/pages/insights/insight-detail</t>
+  </si>
+  <si>
+    <t>到小凡看见详情页面</t>
   </si>
 </sst>
 </file>
@@ -744,7 +759,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -753,6 +768,9 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1">
       <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="49">
@@ -1279,8 +1297,8 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:E7"/>
-  <sheetFormatPr defaultColWidth="9.23076923076923" defaultRowHeight="16.8" outlineLevelRow="6" outlineLevelCol="4"/>
+  <dimension ref="A1:E8"/>
+  <sheetFormatPr defaultColWidth="9.23076923076923" defaultRowHeight="16.8" outlineLevelRow="7" outlineLevelCol="4"/>
   <cols>
     <col min="1" max="1" width="15.1538461538462" customWidth="1"/>
     <col min="2" max="2" width="55.3846153846154" customWidth="1"/>
@@ -1408,6 +1426,23 @@
         <v>25</v>
       </c>
     </row>
+    <row r="8" ht="17" spans="1:5">
+      <c r="A8" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="B8" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="C8" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="D8" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="E8" s="2" t="s">
+        <v>33</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>
